--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -743,14 +743,13 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -767,13 +766,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
 </t>
@@ -809,12 +809,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0226
 </t>
         </is>
       </c>
@@ -826,7 +827,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -836,7 +837,7 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">154
 </t>
@@ -844,7 +845,8 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -861,7 +863,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -886,7 +888,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -898,7 +900,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -910,7 +912,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -928,7 +930,8 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -945,8 +948,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -957,19 +959,19 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -987,19 +989,18 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>616</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -1016,8 +1017,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4316
 </t>
         </is>
       </c>
@@ -1065,13 +1065,13 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1081,10 +1081,16 @@
 </t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">606
+</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1093,9 +1099,9 @@
 </t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1113,7 +1119,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1141,7 +1147,7 @@
 </t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
@@ -1167,12 +1173,12 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1203,12 +1209,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1218,10 +1224,9 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1238,31 +1243,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">502
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">173
 </t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1272,9 +1277,9 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1292,7 +1297,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1304,30 +1309,30 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -1346,26 +1351,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1376,13 +1377,13 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1393,8 +1394,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1403,9 +1403,9 @@
 </t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8656
 </t>
         </is>
       </c>
@@ -1417,13 +1417,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1465,25 +1465,25 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1501,42 +1501,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1547,19 +1542,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1577,7 +1570,8 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1593,7 +1587,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">319
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1616,18 +1611,19 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1652,8 +1648,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1664,7 +1659,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1675,14 +1670,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1693,26 +1686,30 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">447
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1730,8 +1727,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1742,31 +1738,29 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1778,7 +1772,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">8065
 </t>
         </is>
       </c>
@@ -1803,19 +1797,18 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450
+          <t xml:space="preserve">4456
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -1827,7 +1820,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
@@ -1839,13 +1832,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1866,7 +1859,12 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">879
@@ -1885,7 +1883,7 @@
 </t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -1899,7 +1897,8 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1920,7 +1919,7 @@
 </t>
         </is>
       </c>
-      <c r="X11" s="8" t="inlineStr">
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">309
 </t>
@@ -1928,7 +1927,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -1965,8 +1964,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1977,8 +1975,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2019,7 +2016,8 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2030,17 +2028,17 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">722
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -2060,19 +2058,17 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -2090,7 +2086,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -2109,8 +2105,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
-</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -2139,7 +2134,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2157,7 +2152,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -2175,14 +2170,13 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2191,7 +2185,7 @@
 </t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -2203,9 +2197,9 @@
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -2221,7 +2215,7 @@
 </t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -2229,8 +2223,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -2241,8 +2234,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2266,7 +2258,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
@@ -2278,7 +2270,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2288,15 +2280,15 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2314,25 +2306,25 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2356,13 +2348,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2398,7 +2390,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2428,20 +2420,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2470,25 +2459,24 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2536,7 +2524,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2548,19 +2536,18 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2579,19 +2566,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -2633,26 +2620,31 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1609
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9186
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211222
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2663,12 +2655,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t xml:space="preserve">425
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2679,8 +2673,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2691,23 +2684,24 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>464</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2726,7 +2720,9 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t xml:space="preserve">1
+3986
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2743,32 +2739,28 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -2786,7 +2778,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2810,50 +2802,57 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">428
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2869,35 +2868,36 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1373
+          <t xml:space="preserve">432
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2908,13 +2908,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2926,7 +2925,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2938,13 +2937,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
@@ -2956,7 +2955,8 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2967,12 +2967,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>044</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2995,13 +2996,14 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">46
+8 179
 </t>
         </is>
       </c>
@@ -3044,11 +3046,11 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -3056,8 +3058,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3068,8 +3069,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3134,8 +3134,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3146,18 +3145,21 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">212
+44
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">62
+818
 </t>
         </is>
       </c>
@@ -3176,40 +3178,42 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">235
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">3
+1 8 4
+7
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -3221,13 +3225,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -3245,20 +3248,17 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>5352</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -3275,14 +3275,12 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3293,20 +3291,18 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="Z20" s="3" t="n"/>
@@ -3331,8 +3327,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3347,14 +3342,10 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3372,7 +3363,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3384,7 +3375,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3413,19 +3405,19 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">5310
 </t>
         </is>
       </c>
@@ -3437,23 +3429,25 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t xml:space="preserve">259
+8111
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3477,25 +3471,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3506,7 +3499,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -3530,7 +3523,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3542,13 +3535,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8720
 </t>
         </is>
       </c>
@@ -3578,8 +3571,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3590,25 +3582,24 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3633,138 +3624,139 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
-</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8826
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4382
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29526
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1469
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3783,139 +3775,137 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
-</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">531
+          <t>58511</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
+          <t xml:space="preserve">8724
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">469
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -3934,142 +3924,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>814</t>
+          <t xml:space="preserve">748
+</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4087,52 +4077,53 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
-</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>363</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4144,13 +4135,12 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
@@ -4162,19 +4152,19 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -4185,8 +4175,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -4197,7 +4186,8 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -4208,8 +4198,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -4220,7 +4209,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4239,8 +4228,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4257,19 +4245,19 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -4281,7 +4269,8 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -4298,7 +4287,8 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -4309,17 +4299,17 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -4339,25 +4329,24 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
+          <t>61</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -4375,7 +4364,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">16
+54
 </t>
         </is>
       </c>
@@ -4394,17 +4384,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4415,24 +4407,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4444,31 +4437,30 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4486,48 +4478,47 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>081</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4551,14 +4542,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4575,58 +4564,58 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2396
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -4653,22 +4642,21 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -4676,12 +4664,14 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4699,88 +4689,83 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -4807,13 +4792,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>855</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4830,13 +4815,13 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4855,13 +4840,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4879,31 +4863,31 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4914,54 +4898,52 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">032
-</t>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>1136</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">385
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -4985,13 +4967,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5010,19 +4992,19 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">4373
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5034,7 +5016,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5046,31 +5028,37 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -5081,11 +5069,11 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
 </t>
@@ -5105,19 +5093,19 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -5128,19 +5116,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2
+78
 </t>
         </is>
       </c>
@@ -5159,13 +5147,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">32720
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -5177,12 +5165,14 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -5193,110 +5183,100 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5314,8 +5294,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3970
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -5331,7 +5310,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5343,19 +5322,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5373,82 +5352,84 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">832
+</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">54
+5
 </t>
         </is>
       </c>
@@ -5467,144 +5448,136 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
-</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">31
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">786
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">6
+</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5622,144 +5595,139 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">3989
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2890
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="n"/>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">3266
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5778,36 +5746,37 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
+          <t xml:space="preserve">16835
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t xml:space="preserve">561
+</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5819,102 +5788,98 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">1035
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">4325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>836</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -5933,139 +5898,141 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>0029</t>
+          <t xml:space="preserve">3367
+</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">646
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>551</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
-</t>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>444</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3996
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t>6201</t>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">526
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6084,91 +6051,85 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
-</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
+          <t>415</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6180,49 +6141,46 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6240,142 +6198,144 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6393,142 +6353,143 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>0401</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">584
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">001
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6546,144 +6507,144 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4488
+          <t xml:space="preserve">442
+2 6
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>331</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6701,126 +6662,120 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">3413
+</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>663</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>611</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6830,13 +6785,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6854,79 +6809,77 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6938,59 +6891,60 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="S44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -7007,129 +6961,141 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1416
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">777
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18256
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t xml:space="preserve">2424
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1242
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">6 7
+57
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7148,23 +7114,25 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>2401</t>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480
+</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7175,46 +7143,50 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>0564</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8256
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">20 8
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -7231,16 +7203,11 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">690
@@ -7253,28 +7220,29 @@
 </t>
         </is>
       </c>
-      <c r="V46" s="3" t="inlineStr">
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 7
+57
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,36 +737,34 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
-</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">94375
+</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -778,7 +776,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -789,52 +787,51 @@
 </t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0226
-</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -845,8 +842,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -855,24 +851,9 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -886,13 +867,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -900,11 +876,11 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -912,25 +888,20 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -948,10 +919,11 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -959,19 +931,14 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -981,7 +948,7 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
@@ -989,40 +956,38 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n"/>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t xml:space="preserve">741
+</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -1041,11 +1006,10 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4316
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
@@ -1065,43 +1029,38 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1113,37 +1072,36 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2329
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">16089
 </t>
         </is>
       </c>
@@ -1153,13 +1111,13 @@
 </t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
@@ -1167,18 +1125,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -1197,11 +1156,11 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+          <t xml:space="preserve">14373
+</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">330
 </t>
@@ -1209,65 +1168,59 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">502
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">673
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
@@ -1277,9 +1230,9 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1289,7 +1242,7 @@
 </t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -1297,7 +1250,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">20221
 </t>
         </is>
       </c>
@@ -1307,32 +1260,33 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -1351,22 +1305,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12972
+</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>526</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>862</t>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1377,13 +1335,14 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1392,24 +1351,25 @@
 </t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8656
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
@@ -1417,29 +1377,29 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">332
 </t>
@@ -1447,13 +1407,12 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1469,21 +1428,22 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1501,39 +1461,30 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">16665
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1542,58 +1493,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">443
+</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">1943
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
+          <t xml:space="preserve">1963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
+          <t xml:space="preserve">14409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1629
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">16173
+</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">13609
 </t>
         </is>
       </c>
@@ -1605,31 +1559,16 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1648,18 +1587,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3333
+</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1670,12 +1610,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1686,36 +1628,27 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">447
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -1727,40 +1660,42 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1772,13 +1707,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8065
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1797,22 +1732,23 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456
+          <t xml:space="preserve">14450
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1820,7 +1756,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1832,12 +1768,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1847,40 +1784,34 @@
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">1879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1889,9 +1820,9 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9819
 </t>
         </is>
       </c>
@@ -1901,19 +1832,19 @@
 </t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">357
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -1927,16 +1858,11 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1964,10 +1890,11 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
@@ -1975,7 +1902,8 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1986,7 +1914,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1998,14 +1926,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -2028,13 +1955,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2052,27 +1979,28 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>85441</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2844
+</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">304
 </t>
@@ -2080,13 +2008,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2105,10 +2033,11 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+          <t xml:space="preserve">393567
+</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">311
 </t>
@@ -2132,31 +2061,31 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -2176,15 +2105,11 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
@@ -2197,36 +2122,37 @@
 </t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">614
+</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">836
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -2234,12 +2160,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1977
+</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2258,11 +2185,11 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+          <t xml:space="preserve">139740
+</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">325
 </t>
@@ -2270,7 +2197,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2280,45 +2207,40 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2330,7 +2252,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
@@ -2348,13 +2270,13 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2382,7 +2304,7 @@
 </t>
         </is>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -2390,7 +2312,8 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1930
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2420,26 +2343,29 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>441</t>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2453,19 +2379,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2474,15 +2399,10 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2504,7 +2424,7 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -2512,7 +2432,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">1638
 </t>
         </is>
       </c>
@@ -2522,32 +2442,33 @@
 </t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -2566,19 +2487,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">119928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -2590,22 +2511,17 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2614,13 +2530,13 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
@@ -2632,48 +2548,49 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211222
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">11428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
+          <t xml:space="preserve">13687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5334415</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2682,26 +2599,17 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
+          <t xml:space="preserve">14551
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -2720,9 +2628,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-3986
-</t>
+          <t>399</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2737,9 +2643,10 @@
 </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>144</t>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2749,42 +2656,44 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -2794,38 +2703,38 @@
 </t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+          <t>9464</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
+          <t xml:space="preserve">1737
+</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2837,19 +2746,19 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2868,7 +2777,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -2880,40 +2789,38 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2937,17 +2844,17 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -2959,7 +2866,7 @@
 </t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -2967,22 +2874,23 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>631</t>
+          <t xml:space="preserve">1631
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -2996,14 +2904,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-8 179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3022,7 +2929,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4239
+          <t xml:space="preserve">14239
 </t>
         </is>
       </c>
@@ -3038,38 +2945,40 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3078,27 +2987,26 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3122,8 +3030,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3132,9 +3039,10 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>858</t>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -3143,23 +3051,21 @@
 </t>
         </is>
       </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-44
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-818
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3178,21 +3084,23 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -3200,20 +3108,19 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-1 8 4
-7
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3223,24 +3130,25 @@
 </t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24080
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -3248,20 +3156,23 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>5352</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -3275,12 +3186,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t xml:space="preserve">707
+</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3289,23 +3202,30 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t>205</t>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3321,13 +3241,14 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>302</t>
+          <t xml:space="preserve">14335
+</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3342,16 +3263,21 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3361,12 +3287,7 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3375,8 +3296,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3387,17 +3307,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
+          <t xml:space="preserve">1867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">301
 </t>
@@ -3405,19 +3320,19 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -3427,32 +3342,32 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>443</t>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
-8111
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3471,24 +3386,26 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">374 0
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3499,19 +3416,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3523,7 +3440,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3535,19 +3452,19 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3563,7 +3480,7 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -3571,7 +3488,8 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">1564
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -3580,26 +3498,27 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
@@ -3624,28 +3543,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t xml:space="preserve">19255
+</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t xml:space="preserve">1531
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">928
+</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>603</t>
+          <t xml:space="preserve">1603
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3662,101 +3585,83 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1355
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8826
+          <t xml:space="preserve">18828
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4382
+          <t xml:space="preserve">14372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29526
+          <t xml:space="preserve">12952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">11267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14110
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -3775,7 +3680,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t xml:space="preserve">3851
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3790,7 +3696,7 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -3798,12 +3704,13 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -3826,31 +3733,26 @@
 </t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8724
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
+      <c r="Q24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -3870,19 +3772,19 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">1590
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3892,21 +3794,21 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3924,31 +3826,31 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">13740
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>451</t>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3965,16 +3867,11 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3983,13 +3880,13 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -4001,64 +3898,66 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>3243</t>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">9569
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2242
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>661</t>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">17476
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4077,114 +3976,117 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">3298
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>569</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
+          <t>61</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -4192,24 +4094,24 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>661</t>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4228,145 +4130,140 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4384,140 +4281,145 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t xml:space="preserve">93893
+</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1874
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1649
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>081</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4536,59 +4438,61 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
+          <t xml:space="preserve">4085
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2396
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -4598,7 +4502,7 @@
 </t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
@@ -4606,19 +4510,19 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4628,49 +4532,51 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">1626
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t>260</t>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4689,139 +4595,145 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t xml:space="preserve">18564
+</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t xml:space="preserve">1503
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">978
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1919
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1800
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">14419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">11385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">11137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">13328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">18231
+</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">11243
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">13998
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -4840,140 +4752,136 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>064</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t xml:space="preserve">1666
+</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4998,137 +4906,127 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">691
+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-78
+          <t xml:space="preserve">11188
 </t>
         </is>
       </c>
@@ -5147,136 +5045,137 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32720
+          <t xml:space="preserve">13970
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">337
+</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>816</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>495</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t xml:space="preserve">874
+</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+          <t xml:space="preserve">19477
+</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5294,86 +5193,82 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve">3624
+</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5382,11 +5277,11 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -5400,21 +5295,22 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>0554</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
@@ -5422,14 +5318,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-5
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5448,22 +5343,23 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>8845</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+          <t xml:space="preserve">1879
+</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">207
 </t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
@@ -5471,7 +5367,8 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -5480,22 +5377,28 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>241</t>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
+</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5504,24 +5407,24 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>613</t>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">093
+</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -5533,7 +5436,7 @@
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -5563,20 +5466,21 @@
 </t>
         </is>
       </c>
-      <c r="X35" s="3" t="inlineStr">
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5599,18 +5503,19 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -5618,7 +5523,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5642,7 +5547,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5658,15 +5563,15 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -5676,21 +5581,21 @@
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5938
 </t>
         </is>
       </c>
@@ -5706,14 +5611,19 @@
 </t>
         </is>
       </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="inlineStr">
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">050
+</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -5721,13 +5631,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5746,28 +5656,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16835
-</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">561
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116835
+</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5776,7 +5671,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5794,7 +5689,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1608
 </t>
         </is>
       </c>
@@ -5804,53 +5699,47 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4325
+          <t xml:space="preserve">14325
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1154
+</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t xml:space="preserve">1657
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5859,27 +5748,17 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+      <c r="W37" s="3" t="n"/>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">3966
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">3424
 </t>
         </is>
       </c>
@@ -5902,22 +5781,21 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">646
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5926,30 +5804,24 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2111
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5958,30 +5830,31 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5991,7 +5864,7 @@
 </t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="S38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -5999,40 +5872,43 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">1687
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">526
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">793
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6051,7 +5927,8 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t xml:space="preserve">14008
+</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6060,7 +5937,7 @@
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -6086,22 +5963,26 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t xml:space="preserve">525
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>415</t>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -6110,7 +5991,7 @@
 </t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -6118,18 +5999,19 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6141,13 +6023,13 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6156,31 +6038,34 @@
 </t>
         </is>
       </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="W39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6198,19 +6083,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">744
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6222,31 +6107,30 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -6264,25 +6148,25 @@
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Q40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6300,7 +6184,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
@@ -6318,24 +6202,26 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6353,7 +6239,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">14488
 </t>
         </is>
       </c>
@@ -6365,11 +6251,11 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -6377,19 +6263,20 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6400,10 +6287,11 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>0401</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -6417,7 +6305,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6439,7 +6327,7 @@
 </t>
         </is>
       </c>
-      <c r="R41" s="3" t="inlineStr">
+      <c r="R41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -6453,8 +6341,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6465,30 +6352,30 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1740
+</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6507,29 +6394,28 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-2 6
-</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">328
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9249
+</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -6537,114 +6423,114 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
+          <t>028</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1300
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>632</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6662,23 +6548,26 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>186</t>
+          <t xml:space="preserve">23413
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320
+</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6687,7 +6576,7 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -6695,102 +6584,109 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7914
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1828
+</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
@@ -6813,21 +6709,21 @@
 </t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6844,7 +6740,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -6856,98 +6752,82 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">738
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6961,45 +6841,26 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168711
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -7011,91 +6872,71 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18256
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">102342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">16912
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">40844
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="n"/>
+      <c r="W45" s="3" t="n"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1848324382
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -7114,10 +6955,11 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+          <t xml:space="preserve">3117
+</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -7131,7 +6973,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -7141,9 +6983,9 @@
 </t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -7155,31 +6997,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8256
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 8
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -7195,22 +7032,27 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -7222,30 +7064,29 @@
       </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 7
-57
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,34 +737,37 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94375
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9124 11
 </t>
         </is>
       </c>
@@ -776,18 +779,23 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n"/>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 8
+</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -795,19 +803,19 @@
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">1785
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -817,13 +825,13 @@
 </t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -831,7 +839,8 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t xml:space="preserve">637
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -842,7 +851,8 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">277
+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -867,8 +877,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -882,7 +896,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -894,20 +908,15 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -923,19 +932,24 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -948,7 +962,7 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
@@ -956,13 +970,13 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -972,16 +986,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
+          <t xml:space="preserve">7261
 </t>
         </is>
       </c>
@@ -1006,10 +1025,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+          <t xml:space="preserve">8316
+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
@@ -1033,32 +1053,37 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -1072,52 +1097,53 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2329
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16089
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
@@ -1131,13 +1157,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -1156,27 +1182,29 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14373
-</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">1437
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -1184,26 +1212,32 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 82
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1212,15 +1246,15 @@
 </t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">673
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1232,7 +1266,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1242,7 +1276,7 @@
 </t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -1250,7 +1284,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
@@ -1260,27 +1294,22 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+      <c r="W7" s="3" t="n"/>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1779
+          <t xml:space="preserve">17729
 </t>
         </is>
       </c>
@@ -1305,7 +1334,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12972
+          <t xml:space="preserve">989716
 </t>
         </is>
       </c>
@@ -1317,11 +1346,11 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -1341,7 +1370,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1351,13 +1380,13 @@
 </t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -1369,7 +1398,7 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
@@ -1377,29 +1406,29 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">332
 </t>
@@ -1407,7 +1436,8 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t xml:space="preserve">954
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1428,7 +1458,7 @@
 </t>
         </is>
       </c>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -1440,12 +1470,7 @@
 </t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1461,21 +1486,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16665
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">11526
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1484,7 +1520,12 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2112
+</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
@@ -1493,61 +1534,61 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">443
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14409
+          <t xml:space="preserve">18409
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1629
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
+          <t xml:space="preserve">12173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">18319
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13609
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
@@ -1559,16 +1600,26 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">1261
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="3" t="n"/>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114184
+</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -1587,19 +1638,20 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3333
-</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051
+          <t xml:space="preserve">333
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1614,15 +1666,15 @@
 </t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1632,8 +1684,13 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -1645,10 +1702,15 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -1664,13 +1726,13 @@
 </t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -1678,7 +1740,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
@@ -1690,7 +1752,8 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">252
+</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1699,7 +1762,7 @@
 </t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -1707,7 +1770,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
@@ -1732,7 +1795,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14450
+          <t xml:space="preserve">14451
 </t>
         </is>
       </c>
@@ -1748,7 +1811,7 @@
 </t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1768,23 +1831,28 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="n"/>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
@@ -1793,76 +1861,81 @@
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">467
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9819
+          <t xml:space="preserve">23 08
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">357
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
 </t>
         </is>
       </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1878,13 +1951,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3836
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -1894,7 +1966,7 @@
 </t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
@@ -1902,19 +1974,19 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1926,13 +1998,14 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1955,13 +2028,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1979,7 +2052,8 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t xml:space="preserve">854
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1988,19 +2062,19 @@
 </t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2844
-</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
 </t>
@@ -2014,7 +2088,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2033,11 +2107,11 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">393567
-</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+          <t xml:space="preserve">0856
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">311
 </t>
@@ -2061,7 +2135,7 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -2075,17 +2149,17 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+          <t xml:space="preserve">053
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -2105,12 +2179,17 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="8" t="inlineStr">
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -2134,19 +2213,19 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
@@ -2160,13 +2239,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2185,7 +2264,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139740
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -2215,30 +2294,35 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
 </t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
@@ -2252,14 +2336,13 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2276,7 +2359,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2337,7 +2420,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335
+          <t xml:space="preserve">16433
 </t>
         </is>
       </c>
@@ -2349,11 +2432,11 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
@@ -2365,7 +2448,7 @@
 </t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2373,18 +2456,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2396,13 +2480,19 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2424,7 +2514,7 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -2432,7 +2522,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
@@ -2442,15 +2532,15 @@
 </t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2411
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2462,7 +2552,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">17410
 </t>
         </is>
       </c>
@@ -2487,37 +2577,37 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119928
+          <t xml:space="preserve">1992
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
+          <t xml:space="preserve">11299
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">9918
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2536,43 +2626,42 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
-</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">10559
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
+          <t xml:space="preserve">44641
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">11230
 </t>
         </is>
       </c>
@@ -2584,13 +2673,14 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13687
+          <t xml:space="preserve">3687
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>5334415</t>
+          <t xml:space="preserve">531
+</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2599,11 +2689,21 @@
 </t>
         </is>
       </c>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1375
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14551
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
@@ -2628,12 +2728,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -2643,26 +2743,22 @@
 </t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2249
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2673,27 +2769,22 @@
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2703,15 +2794,16 @@
 </t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">861
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>9464</t>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
@@ -2722,7 +2814,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2734,7 +2826,7 @@
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -2777,44 +2869,43 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>8441</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2826,35 +2917,34 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -2866,7 +2956,7 @@
 </t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -2874,7 +2964,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2890,15 +2980,15 @@
 </t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2929,13 +3019,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14239
-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325
+          <t>433</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -2945,21 +3034,21 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2971,13 +3060,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
@@ -2987,7 +3075,7 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -3001,36 +3089,38 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">875
+</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">942
+</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">540
+</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -3041,7 +3131,7 @@
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">6558
 </t>
         </is>
       </c>
@@ -3051,7 +3141,7 @@
 </t>
         </is>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -3059,16 +3149,11 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3084,13 +3169,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
-</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">8568
+</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -3100,9 +3185,9 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -3112,9 +3197,9 @@
 </t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3126,29 +3211,24 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24080
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -3168,11 +3248,11 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="R20" s="8" t="inlineStr">
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -3180,7 +3260,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3192,7 +3272,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">95 1
 </t>
         </is>
       </c>
@@ -3202,7 +3282,7 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
+      <c r="W20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
@@ -3216,7 +3296,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">672
 </t>
         </is>
       </c>
@@ -3241,11 +3321,11 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14335
-</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+          <t xml:space="preserve">433
+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">308
 </t>
@@ -3271,13 +3351,13 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3287,7 +3367,12 @@
 </t>
         </is>
       </c>
-      <c r="K21" s="3" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
@@ -3296,7 +3381,8 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3307,12 +3393,17 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="8" t="inlineStr">
+          <t xml:space="preserve">867
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">301
 </t>
@@ -3332,7 +3423,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -3342,7 +3433,7 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -3350,7 +3441,8 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
@@ -3386,8 +3478,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 0
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3396,19 +3487,14 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+      <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
@@ -3416,11 +3502,11 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">211
 </t>
@@ -3428,7 +3514,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3458,73 +3544,73 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">935
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1564
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3555,19 +3641,19 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">160274
 </t>
         </is>
       </c>
@@ -3585,48 +3671,58 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1355
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18828
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14372
+          <t xml:space="preserve">11372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
+          <t xml:space="preserve">15357
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1462
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11451
+</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3635,7 +3731,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12952
+          <t xml:space="preserve">2952
 </t>
         </is>
       </c>
@@ -3645,17 +3741,27 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2107
+</t>
+        </is>
+      </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11267
+          <t xml:space="preserve">2267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">18110
 </t>
         </is>
       </c>
@@ -3680,13 +3786,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3851
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -3696,63 +3802,73 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">874
 </t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -3772,17 +3888,17 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -3794,21 +3910,17 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="8" t="inlineStr">
+      <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
+      <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3826,36 +3938,37 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13740
+          <t xml:space="preserve">3740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3867,11 +3980,16 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81414 6
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -3884,7 +4002,7 @@
 </t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
 </t>
@@ -3898,22 +4016,23 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">313
 </t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>2431</t>
-        </is>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">040
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -3921,7 +4040,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9569
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
@@ -3933,11 +4052,11 @@
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2242
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -3951,13 +4070,13 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17476
+          <t xml:space="preserve">1748
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -3976,7 +4095,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -3988,8 +4107,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4004,15 +4122,15 @@
 </t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4024,7 +4142,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -4036,24 +4154,25 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4077,16 +4196,17 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -4094,21 +4214,17 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
+      <c r="Y26" s="3" t="n"/>
       <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4130,7 +4246,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9522
 </t>
         </is>
       </c>
@@ -4140,15 +4256,15 @@
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4164,10 +4280,15 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4177,7 +4298,7 @@
 </t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
@@ -4189,7 +4310,7 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -4197,25 +4318,25 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4227,29 +4348,28 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
+          <t xml:space="preserve">098
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
@@ -4263,7 +4383,8 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">54
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4281,7 +4402,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93893
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -4293,8 +4414,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4309,30 +4429,30 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -4347,19 +4467,19 @@
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2813
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4369,7 +4489,7 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
@@ -4383,17 +4503,17 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -4401,8 +4521,7 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="X28" s="8" t="inlineStr">
@@ -4413,7 +4532,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4438,7 +4557,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4085
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
@@ -4450,59 +4569,58 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">203
 </t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
@@ -4516,11 +4634,11 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -4532,9 +4650,9 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2265
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -4550,7 +4668,7 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
+      <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -4562,7 +4680,7 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -4570,7 +4688,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81828
 </t>
         </is>
       </c>
@@ -4595,37 +4713,37 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
+          <t xml:space="preserve">118364
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4643,13 +4761,13 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4661,55 +4779,55 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">91034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14419
+          <t xml:space="preserve">142419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13328
+          <t xml:space="preserve">3328
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18231
+          <t xml:space="preserve">11231
 </t>
         </is>
       </c>
@@ -4721,14 +4839,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11243
-</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13998
-</t>
+          <t>394</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4752,12 +4868,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4769,18 +4885,20 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>1845</t>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1824
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4795,8 +4913,13 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -4810,13 +4933,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>064</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4825,7 +4948,7 @@
 </t>
         </is>
       </c>
-      <c r="Q31" s="8" t="inlineStr">
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
 </t>
@@ -4837,31 +4960,30 @@
 </t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>8458</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
+          <t xml:space="preserve">666
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="W31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -4869,22 +4991,17 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4900,17 +5017,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4373
+          <t xml:space="preserve">9437
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+          <t xml:space="preserve">428
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
@@ -4918,31 +5035,37 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>8651</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4954,11 +5077,11 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -4966,18 +5089,23 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">310
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -4991,24 +5119,25 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">5606
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">682
+</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
@@ -5020,13 +5149,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11188
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5045,48 +5174,54 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13970
+          <t xml:space="preserve">3971
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
@@ -5098,12 +5233,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5119,7 +5255,7 @@
 </t>
         </is>
       </c>
-      <c r="Q33" s="8" t="inlineStr">
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">329
 </t>
@@ -5127,34 +5263,35 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19477
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+          <t xml:space="preserve">477
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
 </t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
@@ -5168,7 +5305,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -5193,13 +5330,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3624
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5215,7 +5352,7 @@
 </t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -5223,13 +5360,13 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5239,9 +5376,10 @@
 </t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">024
+</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5264,11 +5402,16 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">261
@@ -5277,11 +5420,11 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S34" s="8" t="inlineStr">
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -5289,19 +5432,20 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">78868
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>0554</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -5318,13 +5462,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">18328
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5347,19 +5491,19 @@
 </t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
 </t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
@@ -5367,37 +5511,37 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5407,24 +5551,25 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">093
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t xml:space="preserve">834
+</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -5436,7 +5581,7 @@
 </t>
         </is>
       </c>
-      <c r="S35" s="8" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -5450,11 +5595,11 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -5462,11 +5607,11 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="inlineStr">
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
@@ -5480,7 +5625,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5503,16 +5648,15 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>1001</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -5541,13 +5685,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5563,7 +5707,7 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
@@ -5571,7 +5715,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5581,27 +5725,27 @@
 </t>
         </is>
       </c>
-      <c r="Q36" s="8" t="inlineStr">
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">231
 </t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5938
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
@@ -5613,7 +5757,7 @@
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">958
 </t>
         </is>
       </c>
@@ -5625,22 +5769,17 @@
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5660,9 +5799,24 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14501
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1255
+</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">492
@@ -5671,7 +5825,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">92241
 </t>
         </is>
       </c>
@@ -5689,7 +5843,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5699,11 +5853,21 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13965
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14325
+          <t xml:space="preserve">4375
 </t>
         </is>
       </c>
@@ -5715,7 +5879,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5727,18 +5891,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t xml:space="preserve">3437
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
@@ -5748,8 +5913,18 @@
 </t>
         </is>
       </c>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3966
@@ -5758,7 +5933,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -5795,7 +5970,8 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5806,22 +5982,28 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2111
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5830,25 +6012,25 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">19 3
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5864,33 +6046,33 @@
 </t>
         </is>
       </c>
-      <c r="S38" s="8" t="inlineStr">
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">687
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1687
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2 24 2
 </t>
         </is>
       </c>
@@ -5902,13 +6084,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5927,17 +6109,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+          <t xml:space="preserve">140018
+</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -5949,9 +6131,9 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -5961,27 +6143,22 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5991,9 +6168,9 @@
 </t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6003,13 +6180,13 @@
 </t>
         </is>
       </c>
-      <c r="P39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
 </t>
@@ -6017,7 +6194,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -6029,7 +6206,8 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t xml:space="preserve">5345
+</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6038,33 +6216,33 @@
 </t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="V39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="W39" s="8" t="inlineStr">
+      <c r="W39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">1754
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6089,13 +6267,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+          <t>4446</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -6107,11 +6284,11 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+          <t xml:space="preserve">539
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -6119,18 +6296,19 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -6146,9 +6324,9 @@
 </t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6160,11 +6338,11 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
@@ -6184,7 +6362,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -6196,31 +6374,31 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">2172
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6239,14 +6417,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14488
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6267,7 +6444,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -6275,23 +6452,23 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -6327,7 +6504,7 @@
 </t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr">
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -6341,7 +6518,8 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t xml:space="preserve">584
+</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -6352,7 +6530,8 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6363,7 +6542,7 @@
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -6394,12 +6573,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -6409,13 +6589,13 @@
 </t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9249
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -6429,30 +6609,31 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>028</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6464,7 +6645,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6486,7 +6667,7 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
@@ -6494,13 +6675,13 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6512,24 +6693,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">187080
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6548,11 +6730,11 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+          <t xml:space="preserve">441
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">320
 </t>
@@ -6560,7 +6742,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6576,7 +6758,7 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
@@ -6584,13 +6766,13 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6626,17 +6808,17 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="R43" s="8" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -6650,32 +6832,26 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7914
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6686,7 +6862,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6705,17 +6881,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -6723,7 +6899,8 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -6738,9 +6915,9 @@
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -6764,17 +6941,20 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t xml:space="preserve">1890
+</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -6783,15 +6963,15 @@
 </t>
         </is>
       </c>
-      <c r="Q44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6803,19 +6983,19 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8223
 </t>
         </is>
       </c>
@@ -6843,88 +7023,123 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168711
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+          <t xml:space="preserve">188411
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8411
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1056
+</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">28161
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">121804
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101092106191
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102342
+          <t xml:space="preserve">02041
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
+          <t xml:space="preserve">168084
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16912
+          <t xml:space="preserve">12572
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">12917
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">183179
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40844
+          <t xml:space="preserve">448414
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11222
+</t>
+        </is>
+      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848324382
+          <t xml:space="preserve">9247
 </t>
         </is>
       </c>
@@ -6955,11 +7170,11 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
+          <t xml:space="preserve">5117
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -6971,37 +7186,42 @@
 </t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7016,8 +7236,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7032,13 +7251,13 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
-      <c r="R46" s="8" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -7052,7 +7271,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
@@ -7062,7 +7281,7 @@
 </t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -7070,22 +7289,17 @@
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -741,9 +741,9 @@
 </t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -753,7 +753,7 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9124 11
+          <t xml:space="preserve">91124 1
 </t>
         </is>
       </c>
@@ -785,13 +785,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">8 8 8
+</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
@@ -801,9 +801,9 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1785
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -851,7 +851,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -894,9 +894,9 @@
 </t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -908,18 +908,13 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -934,7 +929,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -944,12 +939,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -976,7 +966,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -986,21 +976,21 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">725
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7261
+          <t xml:space="preserve">741
 </t>
         </is>
       </c>
@@ -1025,7 +1015,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316
+          <t xml:space="preserve">4326
 </t>
         </is>
       </c>
@@ -1053,7 +1043,7 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -1061,19 +1051,19 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1127,13 +1117,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1182,19 +1172,19 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1206,19 +1196,19 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1234,27 +1224,27 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">123
 </t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -1309,7 +1299,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17729
+          <t xml:space="preserve">7279
 </t>
         </is>
       </c>
@@ -1334,7 +1324,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989716
+          <t xml:space="preserve">297 6
 </t>
         </is>
       </c>
@@ -1346,28 +1336,28 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">172
 </t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -1394,7 +1384,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1492,13 +1482,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11526
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1522,7 +1512,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -1558,7 +1548,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18409
+          <t xml:space="preserve">4409
 </t>
         </is>
       </c>
@@ -1576,13 +1566,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12173
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18319
+          <t xml:space="preserve">12319
 </t>
         </is>
       </c>
@@ -1610,16 +1600,21 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="3" t="n"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114184
+          <t xml:space="preserve">1141024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -1668,28 +1663,18 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1710,7 +1695,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -1762,7 +1747,7 @@
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -1776,7 +1761,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1795,7 +1780,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14451
+          <t xml:space="preserve">24451
 </t>
         </is>
       </c>
@@ -1823,9 +1808,9 @@
 </t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -1837,13 +1822,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -1859,9 +1844,9 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">467
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -1873,7 +1858,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1885,7 +1870,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 08
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1897,13 +1882,13 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">587
 </t>
         </is>
       </c>
@@ -1915,7 +1900,8 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">247 16
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1932,7 +1918,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -1951,12 +1937,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
+          <t>3833</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1978,9 +1964,9 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1998,7 +1984,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2082,13 +2068,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2107,7 +2093,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2123,9 +2109,9 @@
 </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -2149,13 +2135,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2231,7 +2217,7 @@
 </t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -2239,7 +2225,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -2268,7 +2254,7 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">325
 </t>
@@ -2294,7 +2280,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2304,12 +2290,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+      <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2324,7 +2305,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2342,7 +2323,8 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -2359,7 +2341,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2387,7 +2369,7 @@
 </t>
         </is>
       </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -2395,7 +2377,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -2420,7 +2402,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16433
+          <t xml:space="preserve">433
 </t>
         </is>
       </c>
@@ -2430,9 +2412,9 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">028
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2444,19 +2426,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2468,7 +2450,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">16 8
 </t>
         </is>
       </c>
@@ -2528,7 +2510,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -2552,7 +2534,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17410
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2583,19 +2565,19 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11299
+          <t xml:space="preserve">192499
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9918
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2611,7 +2593,12 @@
 </t>
         </is>
       </c>
-      <c r="I16" s="3" t="n"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2626,30 +2613,30 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
+          <t xml:space="preserve">9246
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10559
+          <t xml:space="preserve">1058
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44641
+          <t xml:space="preserve">4448
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2661,7 +2648,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2728,12 +2715,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">398
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2749,7 +2737,12 @@
 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
@@ -2758,18 +2751,21 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -2784,7 +2780,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2802,7 +2798,7 @@
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">82240
 </t>
         </is>
       </c>
@@ -2814,25 +2810,25 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+          <t xml:space="preserve">737
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">482
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2844,13 +2840,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2869,7 +2865,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2879,45 +2875,49 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>8441</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">713
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n"/>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2934,13 +2934,13 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2974,21 +2974,21 @@
 </t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">506
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3019,12 +3019,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3060,7 +3060,8 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -3099,21 +3100,21 @@
 </t>
         </is>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">618
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3129,9 +3130,9 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6558
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -3149,7 +3150,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -3169,13 +3170,13 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8568
-</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">9568
+</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3187,7 +3188,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3199,7 +3200,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3209,13 +3210,12 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3236,19 +3236,19 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3260,13 +3260,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
+          <t xml:space="preserve">7072
 </t>
         </is>
       </c>
@@ -3284,8 +3284,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3369,7 +3368,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3427,9 +3426,9 @@
 </t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">089
 </t>
         </is>
       </c>
@@ -3453,7 +3452,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">8508
 </t>
         </is>
       </c>
@@ -3478,7 +3477,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>344</t>
+          <t xml:space="preserve">3741
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3487,7 +3487,11 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -3496,7 +3500,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
@@ -3506,9 +3510,9 @@
 </t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3586,17 +3590,17 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">935
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -3610,7 +3614,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3635,13 +3639,13 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3653,7 +3657,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160274
+          <t xml:space="preserve">6059
 </t>
         </is>
       </c>
@@ -3677,7 +3681,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">4953
 </t>
         </is>
       </c>
@@ -3701,25 +3705,25 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11372
+          <t xml:space="preserve">4372
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15357
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11451
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
@@ -3743,13 +3747,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2107
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3761,7 +3765,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -3786,17 +3790,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -3804,7 +3808,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -3816,7 +3820,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3828,7 +3832,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3852,7 +3856,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3864,13 +3868,13 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23 8
 </t>
         </is>
       </c>
@@ -3944,19 +3948,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -3968,40 +3972,40 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 6
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81414 6
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4010,25 +4014,25 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">31 5
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4040,17 +4044,17 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -4062,7 +4066,7 @@
 </t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4076,7 +4080,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -4134,9 +4138,9 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4160,7 +4164,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">89 2
 </t>
         </is>
       </c>
@@ -4190,7 +4194,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -4202,7 +4206,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4246,25 +4250,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522
+          <t xml:space="preserve">3548
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4274,7 +4277,7 @@
 </t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -4282,7 +4285,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4318,7 +4321,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
@@ -4336,7 +4339,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4352,20 +4355,20 @@
 </t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">006
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
+          <t>634</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -4377,7 +4380,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4402,7 +4405,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4414,7 +4417,8 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4425,19 +4429,19 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4465,9 +4469,9 @@
 </t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2813
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -4479,7 +4483,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4509,7 +4513,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4521,10 +4525,10 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
+          <t>9561</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -4532,7 +4536,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -4557,30 +4561,29 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4622,7 +4625,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4634,7 +4637,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4650,7 +4653,7 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -4658,7 +4661,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1626
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4680,7 +4683,7 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
+      <c r="X29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -4688,13 +4691,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81828
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4713,7 +4716,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118364
+          <t xml:space="preserve">118564
 </t>
         </is>
       </c>
@@ -4725,13 +4728,13 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -4749,7 +4752,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4767,7 +4770,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">9296
 </t>
         </is>
       </c>
@@ -4779,25 +4782,25 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91034
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142419
+          <t xml:space="preserve">4419
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">2385
 </t>
         </is>
       </c>
@@ -4821,13 +4824,13 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4839,12 +4842,12 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>613</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>439</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4868,19 +4871,18 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>096</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4897,7 +4899,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4913,13 +4915,8 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -4939,12 +4936,13 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">884
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4962,7 +4960,8 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4973,13 +4972,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8246
 </t>
         </is>
       </c>
@@ -4991,13 +4990,13 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5017,13 +5016,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1437
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5035,7 +5034,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -5053,7 +5052,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5065,83 +5064,83 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">884
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5606
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">682
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -5155,7 +5154,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -5174,13 +5173,12 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3971
-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5190,9 +5188,9 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">657
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5204,14 +5202,13 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5219,9 +5216,9 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">011
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5261,9 +5258,9 @@
 </t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
@@ -5305,13 +5302,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">17276
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5336,7 +5333,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -5352,7 +5349,7 @@
 </t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -5376,9 +5373,9 @@
 </t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">024
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5420,7 +5417,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5432,17 +5429,17 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78868
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -5454,7 +5451,7 @@
 </t>
         </is>
       </c>
-      <c r="X34" s="8" t="inlineStr">
+      <c r="X34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
@@ -5462,7 +5459,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18328
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5487,7 +5484,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -5553,13 +5550,13 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5595,19 +5592,19 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5619,13 +5616,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5656,10 +5653,10 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -5667,13 +5664,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19 0 1
 </t>
         </is>
       </c>
@@ -5691,7 +5688,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -5709,7 +5706,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5745,7 +5742,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -5757,19 +5754,19 @@
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
-      <c r="W36" s="8" t="inlineStr">
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5801,19 +5798,19 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14501
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -5825,7 +5822,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92241
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5855,13 +5852,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5879,7 +5876,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1396
 </t>
         </is>
       </c>
@@ -5891,7 +5888,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">12560
 </t>
         </is>
       </c>
@@ -5982,7 +5979,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5994,13 +5991,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6048,7 +6044,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6060,7 +6056,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -6072,7 +6068,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 24 2
+          <t xml:space="preserve">224 1
 </t>
         </is>
       </c>
@@ -6084,7 +6080,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">793
 </t>
         </is>
       </c>
@@ -6109,13 +6105,13 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140018
-</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">4008
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -6133,20 +6129,20 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">585
+</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6158,7 +6154,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6168,9 +6164,9 @@
 </t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -6182,31 +6178,31 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5345
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6230,19 +6226,19 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1754
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6265,9 +6261,9 @@
 </t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>4446</t>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>91</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -6284,109 +6280,109 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">083
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2172
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -6398,7 +6394,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -6417,13 +6413,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>943</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -6432,7 +6428,7 @@
 </t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -6444,7 +6440,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -6452,19 +6448,19 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6542,13 +6538,13 @@
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -6573,13 +6569,13 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">14645
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -6615,7 +6611,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6667,24 +6663,24 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">222
 </t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">500
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">275
@@ -6697,15 +6693,15 @@
 </t>
         </is>
       </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187080
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -6730,7 +6726,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -6772,7 +6768,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6808,7 +6804,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -6836,7 +6832,12 @@
 </t>
         </is>
       </c>
-      <c r="U43" s="3" t="n"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">230
@@ -6851,7 +6852,7 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>531</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6881,7 +6882,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -6915,15 +6916,15 @@
 </t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6939,28 +6940,26 @@
 </t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">098
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -6971,7 +6970,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6983,28 +6982,23 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8223
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
@@ -7023,43 +7017,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188411
+          <t xml:space="preserve">1682111
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
+          <t xml:space="preserve">8251
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1833
 </t>
         </is>
       </c>
@@ -7071,87 +7064,92 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28161
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121804
+          <t xml:space="preserve">19104
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101092106191
+          <t xml:space="preserve">100921059
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02041
+          <t xml:space="preserve">0342
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168084
+          <t xml:space="preserve">1404
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12572
+          <t xml:space="preserve">2575
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12917
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183179
+          <t xml:space="preserve">13820
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448414
+          <t xml:space="preserve">4840
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1822
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">815
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11222
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9247
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -7170,7 +7168,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
+          <t xml:space="preserve">3117
 </t>
         </is>
       </c>
@@ -7192,9 +7190,9 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -7204,9 +7202,9 @@
 </t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7218,7 +7216,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -7236,7 +7234,8 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>605</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7253,7 +7252,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -7287,13 +7286,13 @@
 </t>
         </is>
       </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
@@ -753,9 +753,9 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91124 1
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -785,17 +785,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 8 8
-</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -851,11 +851,11 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -879,7 +879,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>621</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -908,13 +908,23 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n"/>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -939,7 +949,12 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
@@ -952,7 +967,7 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
@@ -966,7 +981,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1015,8 +1030,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4326
-</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1031,7 +1045,7 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -1051,17 +1065,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">006
 </t>
@@ -1123,7 +1137,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1182,12 +1196,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">250
@@ -1202,13 +1211,13 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1220,31 +1229,31 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
@@ -1256,7 +1265,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1274,7 +1283,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
@@ -1290,8 +1299,13 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -1299,13 +1313,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7279
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1324,11 +1338,11 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297 6
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">326
 </t>
@@ -1336,8 +1350,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1346,7 +1359,7 @@
 </t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -1384,7 +1397,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1432,7 +1445,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1450,17 +1463,22 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1752
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1482,25 +1500,25 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">8526
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">8225
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1512,7 +1530,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1524,7 +1542,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -1566,13 +1584,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">16173
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12319
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -1602,19 +1620,19 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141024
+          <t xml:space="preserve">4024
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1663,18 +1681,28 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -1711,7 +1739,7 @@
 </t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -1780,7 +1808,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24451
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1796,7 +1824,7 @@
 </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">243
 </t>
@@ -1804,13 +1832,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1822,13 +1850,13 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1846,68 +1874,66 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25 8
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">587
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247 16
-</t>
-        </is>
-      </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1937,10 +1963,11 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>3833</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -1966,7 +1993,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1984,7 +2011,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2014,7 +2041,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -2060,7 +2087,7 @@
 </t>
         </is>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">304
 </t>
@@ -2068,7 +2095,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">11977
 </t>
         </is>
       </c>
@@ -2093,7 +2120,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -2109,9 +2136,9 @@
 </t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">355
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2231,7 +2258,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2250,7 +2277,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -2280,7 +2307,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2290,7 +2317,12 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">57
@@ -2303,9 +2335,9 @@
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -2323,7 +2355,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2351,7 +2383,7 @@
 </t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -2369,7 +2401,7 @@
 </t>
         </is>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -2377,8 +2409,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2402,7 +2433,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
+          <t xml:space="preserve">1433
 </t>
         </is>
       </c>
@@ -2412,9 +2443,9 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
 </t>
         </is>
       </c>
@@ -2432,7 +2463,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2450,7 +2481,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2460,9 +2491,9 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2510,11 +2541,11 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -2526,7 +2557,7 @@
 </t>
         </is>
       </c>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
@@ -2540,7 +2571,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2559,13 +2590,13 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992
+          <t xml:space="preserve">19928
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192499
+          <t xml:space="preserve">1499
 </t>
         </is>
       </c>
@@ -2583,54 +2614,48 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9246
+          <t xml:space="preserve">1946
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1058
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4448
+          <t xml:space="preserve">4441
 </t>
         </is>
       </c>
@@ -2648,13 +2673,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">10425
 </t>
         </is>
       </c>
@@ -2684,8 +2709,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2715,7 +2739,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">3998
 </t>
         </is>
       </c>
@@ -2739,31 +2763,38 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115515
+</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -2780,7 +2811,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -2796,13 +2827,13 @@
 </t>
         </is>
       </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82240
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
 </t>
@@ -2810,7 +2841,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
@@ -2828,7 +2859,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2865,13 +2896,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -2883,7 +2913,8 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2894,19 +2925,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2917,30 +2948,31 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -2964,7 +2996,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -2980,15 +3012,15 @@
 </t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3019,7 +3051,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t xml:space="preserve">22234
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3060,13 +3093,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -3076,9 +3109,9 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3102,7 +3135,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -3154,7 +3187,11 @@
 </t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3170,8 +3207,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9568
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -3194,7 +3230,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -3210,10 +3246,16 @@
 </t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -3236,7 +3278,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3248,13 +3290,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
@@ -3266,13 +3308,13 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7072
+          <t xml:space="preserve">707
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 1
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3284,7 +3326,8 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3372,7 +3415,7 @@
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -3380,7 +3423,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3398,7 +3441,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3422,13 +3465,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3452,7 +3495,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8508
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -3477,11 +3520,11 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741
-</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+          <t xml:space="preserve">23746
+</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">318
 </t>
@@ -3489,25 +3532,25 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2475
 </t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -3534,9 +3577,9 @@
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3578,7 +3621,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">2564
 </t>
         </is>
       </c>
@@ -3588,9 +3631,9 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -3633,13 +3676,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19255
+          <t xml:space="preserve">1925
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
@@ -3657,7 +3700,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6059
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -3675,13 +3718,13 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4953
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -3717,61 +3760,60 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2952
+          <t xml:space="preserve">28952
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3790,7 +3832,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">13985
 </t>
         </is>
       </c>
@@ -3800,7 +3842,7 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -3808,19 +3850,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -3856,7 +3898,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3874,7 +3916,7 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3886,7 +3928,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 8
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3898,7 +3940,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -3920,7 +3962,12 @@
 </t>
         </is>
       </c>
-      <c r="Y24" s="3" t="n"/>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">54
@@ -3942,23 +3989,23 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3740
+          <t xml:space="preserve">23740
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">257
 </t>
@@ -3978,8 +4025,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3990,7 +4036,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4014,31 +4060,31 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 5
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4050,7 +4096,7 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -4066,7 +4112,7 @@
 </t>
         </is>
       </c>
-      <c r="X25" s="3" t="inlineStr">
+      <c r="X25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4080,7 +4126,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -4099,7 +4145,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292
+          <t xml:space="preserve">3298
 </t>
         </is>
       </c>
@@ -4111,7 +4157,8 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4128,7 +4175,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -4138,9 +4185,9 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4164,7 +4211,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89 2
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4194,41 +4241,46 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="X26" s="3" t="inlineStr">
+      <c r="X26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="Y26" s="3" t="n"/>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -4250,13 +4302,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3548
+          <t xml:space="preserve">13544
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4277,7 +4329,7 @@
 </t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -4285,7 +4337,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4321,7 +4373,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -4355,15 +4407,16 @@
 </t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
@@ -4380,8 +4433,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4405,7 +4457,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">3893
 </t>
         </is>
       </c>
@@ -4453,7 +4505,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -4513,11 +4565,11 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -4525,7 +4577,8 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
@@ -4542,8 +4595,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4567,12 +4619,14 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4583,7 +4637,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4595,7 +4649,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4607,7 +4661,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4623,7 +4677,7 @@
 </t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -4637,7 +4691,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4653,7 +4707,7 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -4661,7 +4715,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -4671,7 +4725,7 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -4716,20 +4770,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118564
+          <t xml:space="preserve">18564
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">1503
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -4740,13 +4793,13 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">1525
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
@@ -4770,7 +4823,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9296
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4782,7 +4835,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
@@ -4800,7 +4853,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2385
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -4824,7 +4877,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4842,12 +4895,14 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t xml:space="preserve">1243
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>439</t>
+          <t xml:space="preserve">3998
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4871,23 +4926,25 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">371
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>096</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4905,17 +4962,22 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4958,7 +5020,7 @@
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -4966,7 +5028,7 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -4976,9 +5038,9 @@
 </t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8246
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -4990,17 +5052,22 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5016,13 +5083,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1437
+          <t xml:space="preserve">457
 </t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">3528
 </t>
         </is>
       </c>
@@ -5032,13 +5099,13 @@
 </t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">669
+</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">126
 </t>
@@ -5052,7 +5119,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5064,7 +5131,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5082,7 +5149,7 @@
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5094,8 +5161,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5124,11 +5190,11 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -5136,7 +5202,7 @@
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5148,13 +5214,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5173,12 +5239,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">3979
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
@@ -5213,12 +5280,13 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5258,9 +5326,9 @@
 </t>
         </is>
       </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">389
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5272,17 +5340,17 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">477
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -5302,13 +5370,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17276
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5327,7 +5395,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
+          <t xml:space="preserve">13624
 </t>
         </is>
       </c>
@@ -5357,7 +5425,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5369,13 +5437,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5439,7 +5507,7 @@
 </t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
+      <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -5459,7 +5527,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -5514,7 +5582,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5538,7 +5606,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5550,7 +5618,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5592,13 +5660,13 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5645,7 +5713,7 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -5653,7 +5721,8 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5668,9 +5737,9 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 0 1
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5682,13 +5751,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5706,7 +5775,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -5752,9 +5821,9 @@
 </t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5766,7 +5835,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5776,7 +5845,11 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5792,7 +5865,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116835
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
@@ -5804,19 +5877,19 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
@@ -5840,7 +5913,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
@@ -5858,7 +5931,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
@@ -5888,7 +5961,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12560
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -5949,7 +6022,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3367
+          <t xml:space="preserve">23267
 </t>
         </is>
       </c>
@@ -5965,7 +6038,7 @@
 </t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">251
 </t>
@@ -5991,7 +6064,8 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -6008,13 +6082,13 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 3
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -6044,7 +6118,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6056,7 +6130,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -6068,7 +6142,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 1
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6086,7 +6160,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6105,7 +6179,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">14008
 </t>
         </is>
       </c>
@@ -6127,19 +6201,24 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">139
@@ -6166,7 +6245,7 @@
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6178,13 +6257,13 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
@@ -6196,7 +6275,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6218,7 +6297,7 @@
 </t>
         </is>
       </c>
-      <c r="W39" s="3" t="inlineStr">
+      <c r="W39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
@@ -6261,18 +6340,19 @@
 </t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>91</t>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841
+</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
@@ -6280,13 +6360,13 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -6322,7 +6402,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -6368,15 +6448,15 @@
 </t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">083
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6388,13 +6468,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
@@ -6413,22 +6493,23 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
+          <t xml:space="preserve">2448
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -6448,7 +6529,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -6536,7 +6617,7 @@
 </t>
         </is>
       </c>
-      <c r="X41" s="8" t="inlineStr">
+      <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -6550,7 +6631,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6569,7 +6650,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14645
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -6591,7 +6672,7 @@
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -6623,7 +6704,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6647,7 +6728,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6663,15 +6744,15 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">1500
 </t>
         </is>
       </c>
@@ -6689,25 +6770,25 @@
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -6726,7 +6807,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">23413
 </t>
         </is>
       </c>
@@ -6738,7 +6819,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -6748,7 +6829,7 @@
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">134
 </t>
@@ -6790,7 +6871,7 @@
 </t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="N43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
@@ -6798,13 +6879,13 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6820,7 +6901,7 @@
 </t>
         </is>
       </c>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">254
 </t>
@@ -6834,7 +6915,7 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6852,12 +6933,12 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -6898,7 +6979,7 @@
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -6924,7 +7005,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6934,32 +7015,33 @@
 </t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">041
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -6982,23 +7064,28 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
         </is>
       </c>
-      <c r="W44" s="3" t="n"/>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
@@ -7017,42 +7104,42 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682111
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8251
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t xml:space="preserve">1056
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1833
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -7064,27 +7151,31 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19104
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1092
+</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100921059
+          <t xml:space="preserve">12181
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0342
-</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -7095,55 +7186,50 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2575
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13820
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">483904
 </t>
         </is>
       </c>
@@ -7180,7 +7266,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7190,15 +7276,15 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">041
 </t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
@@ -7214,12 +7300,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -7240,7 +7321,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -7252,7 +7333,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -7286,13 +7367,13 @@
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="inlineStr">
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="inlineStr">
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,128 +728,107 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1242
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">637
-</t>
+          <t>637</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
       <c r="X4" s="3" t="n"/>
@@ -884,135 +854,113 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">741
-</t>
+          <t>741</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1035,140 +983,117 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">006
-</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
+          <t>886</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
-</t>
+          <t>619</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1186,141 +1111,118 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
-</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>779</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1338,14 +1240,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>326</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1355,128 +1255,107 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1752
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1494,146 +1373,122 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8526
-</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225
-</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4409
-</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16173
-</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
-</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
-</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4024
-</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1651,146 +1506,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">876
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1808,104 +1639,87 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>243</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1915,20 +1729,17 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
@@ -1938,14 +1749,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1963,146 +1772,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">304
-</t>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>304</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11977
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2120,146 +1905,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2277,134 +2038,112 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">509
-</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>216</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2414,8 +2153,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2433,146 +2171,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">028
-</t>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>638</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>228</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2590,26 +2304,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19928
-</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1499
-</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2619,20 +2329,17 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2643,68 +2350,57 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4441
-</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3687
-</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2714,14 +2410,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
-</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2739,146 +2433,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115515
-</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>202</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2901,38 +2571,32 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2942,98 +2606,82 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3051,140 +2699,117 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22234
-</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3212,140 +2837,117 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2415
-</t>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3363,146 +2965,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">433
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3520,32 +3098,27 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23746
-</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2475
-</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3555,110 +3128,92 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3676,110 +3231,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1925
-</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4372
-</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28952
-</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3789,32 +3326,27 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3832,146 +3364,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13985
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3989,38 +3497,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23740
-</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -4030,104 +3532,87 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>226</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4145,146 +3630,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298
-</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4302,8 +3763,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13544
-</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -4313,122 +3773,102 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -4438,8 +3878,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4457,140 +3896,117 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3893
-</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>260</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4613,146 +4029,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>255</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4770,14 +4162,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18564
-</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503
-</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4787,128 +4177,107 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1525
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419
-</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3328
-</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3998
-</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4926,146 +4295,122 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5083,80 +4428,67 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">457
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3528
-</t>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">669
-</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -5166,62 +4498,52 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>237</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5239,38 +4561,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3979
-</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
+          <t>337</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -5280,104 +4596,87 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1477
-</t>
+          <t>477</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>258</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5395,146 +4694,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13624
-</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
-</t>
+          <t>873</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5552,146 +4827,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>879</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5709,140 +4960,117 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3989
-</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -5865,146 +5093,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
-</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
-</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4375
-</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1396
-</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437
-</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3966
-</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6022,146 +5226,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23267
-</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>251</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">793
-</t>
+          <t>793</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6179,146 +5359,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>238</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6336,146 +5492,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
-</t>
+          <t>813</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6493,146 +5625,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
-</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>245</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">584
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6650,146 +5758,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>258</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6807,128 +5891,107 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>254</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>814</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6938,14 +6001,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6963,74 +6024,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
-</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">041
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -7040,50 +6089,42 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X44" s="3" t="n"/>
@@ -7109,68 +6150,57 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
-</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
-</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12181
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -7180,63 +6210,53 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
-</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483904
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7254,129 +6274,112 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">041
-</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1676
-</t>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>247</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n"/>

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>222</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>328</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>310</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>155</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3389,34 +3389,34 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>193</t>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>913</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5625,17 +5625,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>574</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>224</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>282</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_digit_manipulation.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>919</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>649</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>584</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6284,49 +6284,49 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>202</t>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
